--- a/cv/citations/publications.xlsx
+++ b/cv/citations/publications.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="publications" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'publications'!$A$1:$K$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'publications'!$A$1:$K$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1017,8 +1017,53 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Sep</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr"/>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Global Ecology and Conservation</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>Integrating unmanned aerial vehicle-derived habitat metrics with movement persistence and species distribution models to characterize seasonal habitat use of invasive turtles in urban wetlands</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>Kim, Yonghwan and Lee, Seunghyeon and Shin, Wonhyeop and Song, Youngkeun</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>e04430</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t>10.1016/j.gecco.2026.e04430</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K11"/>
+  <autoFilter ref="A1:K12"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K3" r:id="rId2"/>
@@ -1030,6 +1075,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
